--- a/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,74; 62,83</t>
+          <t>44,59; 63,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,49; 52,42</t>
+          <t>31,76; 52,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 16,69</t>
+          <t>-2,4; 16,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,85; 68,29</t>
+          <t>51,46; 67,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 57,76</t>
+          <t>37,05; 57,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 26,26</t>
+          <t>-1,62; 25,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,11; 63,97</t>
+          <t>51,57; 63,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,84; 51,66</t>
+          <t>37,2; 52,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 18,17</t>
+          <t>0,32; 17,99</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>129,54; 293,77</t>
+          <t>131,12; 297,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,79; 238,21</t>
+          <t>96,18; 231,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 74,93</t>
+          <t>-9,4; 73,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149,26; 311,49</t>
+          <t>150,02; 304,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>113,4; 259,85</t>
+          <t>111,75; 267,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 115,19</t>
+          <t>-5,99; 108,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>154,95; 266,5</t>
+          <t>160,14; 270,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>116,15; 215,98</t>
+          <t>118,44; 220,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 72,75</t>
+          <t>-0,7; 70,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,34; 59,69</t>
+          <t>43,59; 60,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,08; 48,13</t>
+          <t>30,74; 48,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 17,84</t>
+          <t>-0,4; 18,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,57; 59,22</t>
+          <t>43,87; 59,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,92; 56,93</t>
+          <t>40,89; 56,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 23,92</t>
+          <t>6,66; 24,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,52; 57,6</t>
+          <t>46,23; 57,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,31; 50,23</t>
+          <t>39,19; 50,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 18,05</t>
+          <t>6,02; 19,01</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>125,5; 239,89</t>
+          <t>123,7; 245,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,55; 196,45</t>
+          <t>84,14; 190,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 69,38</t>
+          <t>-1,33; 71,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126,35; 248,47</t>
+          <t>125,54; 255,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>119,0; 239,22</t>
+          <t>119,53; 231,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,81; 100,11</t>
+          <t>19,41; 97,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>137,6; 221,65</t>
+          <t>139,07; 222,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>114,97; 195,04</t>
+          <t>116,67; 194,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 68,11</t>
+          <t>17,86; 72,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,26; 62,8</t>
+          <t>45,42; 62,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,95; 35,45</t>
+          <t>15,77; 34,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -1,27</t>
+          <t>-19,86; -0,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,1; 64,13</t>
+          <t>47,38; 64,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 32,5</t>
+          <t>12,46; 32,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -2,34</t>
+          <t>-19,12; -1,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,35; 61,4</t>
+          <t>49,38; 60,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,61; 31,2</t>
+          <t>17,31; 31,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -4,02</t>
+          <t>-17,62; -4,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>128,28; 263,3</t>
+          <t>129,1; 263,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,19; 144,91</t>
+          <t>44,64; 140,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,35; -5,55</t>
+          <t>-59,58; -3,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126,85; 265,02</t>
+          <t>129,14; 260,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,41; 125,7</t>
+          <t>35,61; 127,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,19; -9,17</t>
+          <t>-53,35; -3,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>144,5; 239,59</t>
+          <t>142,54; 235,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52,73; 119,42</t>
+          <t>51,54; 117,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,99; -14,76</t>
+          <t>-52,75; -16,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,45; 53,18</t>
+          <t>36,76; 53,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,96; 45,7</t>
+          <t>28,0; 44,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 4,56</t>
+          <t>-13,12; 4,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39,22; 55,5</t>
+          <t>37,96; 54,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,92; 47,44</t>
+          <t>28,82; 46,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 8,53</t>
+          <t>-10,39; 7,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,08; 51,83</t>
+          <t>40,07; 51,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,07; 42,66</t>
+          <t>31,16; 43,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 2,95</t>
+          <t>-9,1; 3,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,73; 172,85</t>
+          <t>88,98; 173,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65,09; 146,0</t>
+          <t>67,28; 145,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 14,63</t>
+          <t>-32,22; 16,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102,26; 207,64</t>
+          <t>103,77; 199,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>78,35; 172,29</t>
+          <t>76,96; 167,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 30,44</t>
+          <t>-28,19; 25,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>102,94; 169,28</t>
+          <t>103,55; 169,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>79,92; 137,71</t>
+          <t>81,5; 137,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 9,64</t>
+          <t>-23,82; 11,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,51; 55,17</t>
+          <t>46,57; 55,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,47; 40,94</t>
+          <t>31,62; 41,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,0</t>
+          <t>-6,9; 4,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49,08; 57,45</t>
+          <t>48,94; 57,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,91; 43,83</t>
+          <t>34,55; 44,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,47</t>
+          <t>-0,74; 8,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,15; 55,11</t>
+          <t>49,2; 55,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,83; 41,33</t>
+          <t>34,7; 41,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,52</t>
+          <t>-1,92; 5,43</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>134,61; 191,51</t>
+          <t>132,73; 193,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>91,9; 141,24</t>
+          <t>91,34; 144,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 13,64</t>
+          <t>-20,11; 14,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147,63; 211,23</t>
+          <t>147,56; 210,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>106,73; 158,7</t>
+          <t>105,35; 160,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 33,79</t>
+          <t>-1,94; 31,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>150,17; 191,79</t>
+          <t>148,36; 189,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>106,02; 143,69</t>
+          <t>104,85; 141,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 18,81</t>
+          <t>-5,99; 18,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,59; 63,6</t>
+          <t>44,07; 62,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,76; 52,47</t>
+          <t>30,92; 52,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 16,87</t>
+          <t>-3,15; 17,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,46; 67,79</t>
+          <t>52,89; 69,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,05; 57,18</t>
+          <t>35,95; 56,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 25,25</t>
+          <t>-2,5; 26,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,57; 63,72</t>
+          <t>50,73; 63,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,2; 52,34</t>
+          <t>37,99; 51,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 17,99</t>
+          <t>1,06; 18,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>131,12; 297,29</t>
+          <t>132,17; 280,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>96,18; 231,2</t>
+          <t>92,69; 236,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 73,96</t>
+          <t>-10,18; 75,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150,02; 304,49</t>
+          <t>155,71; 316,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>111,75; 267,42</t>
+          <t>109,08; 255,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 108,61</t>
+          <t>-8,46; 114,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>160,14; 270,53</t>
+          <t>158,85; 264,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>118,44; 220,33</t>
+          <t>121,46; 218,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 70,19</t>
+          <t>3,0; 75,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,59; 60,09</t>
+          <t>43,23; 59,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,74; 48,16</t>
+          <t>31,45; 48,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 18,37</t>
+          <t>-0,21; 18,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,87; 59,49</t>
+          <t>43,75; 58,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,89; 56,12</t>
+          <t>40,64; 55,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 24,2</t>
+          <t>7,2; 23,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,23; 57,61</t>
+          <t>46,36; 57,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,19; 50,42</t>
+          <t>39,06; 51,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 19,01</t>
+          <t>6,33; 18,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>123,7; 245,04</t>
+          <t>117,75; 238,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,14; 190,78</t>
+          <t>88,31; 196,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 71,97</t>
+          <t>-0,73; 68,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125,54; 255,01</t>
+          <t>125,54; 245,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>119,53; 231,49</t>
+          <t>115,99; 228,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 97,16</t>
+          <t>19,25; 94,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>139,07; 222,37</t>
+          <t>139,09; 225,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>116,67; 194,27</t>
+          <t>117,4; 195,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 72,98</t>
+          <t>18,77; 70,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,42; 62,75</t>
+          <t>46,39; 63,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,77; 34,87</t>
+          <t>15,42; 36,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,86; -0,55</t>
+          <t>-20,0; -0,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,38; 64,04</t>
+          <t>47,24; 64,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 32,49</t>
+          <t>11,81; 31,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,12; -1,07</t>
+          <t>-19,62; -1,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,38; 60,72</t>
+          <t>48,8; 60,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,31; 31,23</t>
+          <t>16,65; 30,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,62; -4,68</t>
+          <t>-17,15; -4,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129,1; 263,59</t>
+          <t>130,06; 278,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,64; 140,47</t>
+          <t>44,97; 149,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,58; -3,52</t>
+          <t>-60,98; -3,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129,14; 260,08</t>
+          <t>125,1; 257,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,61; 127,63</t>
+          <t>33,2; 127,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,35; -3,34</t>
+          <t>-54,17; -7,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>142,54; 235,44</t>
+          <t>140,62; 233,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,54; 117,34</t>
+          <t>47,81; 119,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,75; -16,68</t>
+          <t>-50,87; -14,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,76; 53,16</t>
+          <t>35,77; 53,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,0; 44,86</t>
+          <t>27,22; 45,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 4,95</t>
+          <t>-13,58; 4,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,96; 54,56</t>
+          <t>39,13; 55,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,82; 46,27</t>
+          <t>29,14; 45,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 7,42</t>
+          <t>-9,68; 6,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,07; 51,98</t>
+          <t>40,64; 52,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,16; 43,14</t>
+          <t>31,01; 43,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 3,45</t>
+          <t>-9,05; 3,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,98; 173,92</t>
+          <t>85,24; 173,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,28; 145,3</t>
+          <t>64,21; 149,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 16,88</t>
+          <t>-32,43; 14,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103,77; 199,05</t>
+          <t>105,56; 198,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,96; 167,59</t>
+          <t>78,52; 164,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 25,64</t>
+          <t>-26,01; 23,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>103,55; 169,26</t>
+          <t>105,8; 170,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,5; 137,83</t>
+          <t>80,79; 139,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 11,06</t>
+          <t>-24,45; 10,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,57; 55,47</t>
+          <t>46,41; 55,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,62; 41,35</t>
+          <t>31,65; 41,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 4,15</t>
+          <t>-6,32; 4,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48,94; 57,36</t>
+          <t>49,61; 57,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,55; 44,17</t>
+          <t>34,79; 43,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,84</t>
+          <t>-0,65; 8,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,2; 55,04</t>
+          <t>49,4; 55,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,13</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,43</t>
+          <t>-1,66; 5,66</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>132,73; 193,69</t>
+          <t>134,55; 195,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>91,34; 144,81</t>
+          <t>89,73; 141,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 14,21</t>
+          <t>-18,89; 13,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147,56; 210,6</t>
+          <t>148,1; 207,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>105,35; 160,46</t>
+          <t>107,23; 158,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 31,66</t>
+          <t>-2,1; 31,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>148,36; 189,84</t>
+          <t>149,52; 190,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>104,85; 141,51</t>
+          <t>106,43; 144,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 18,29</t>
+          <t>-5,06; 19,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60,61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47,35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>54,32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>42,61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,86</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47,35</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,5</t>
+          <t>9,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,07; 62,55</t>
+          <t>51,85; 68,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,92; 52,9</t>
+          <t>36,53; 57,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 17,15</t>
+          <t>-0,12; 26,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,89; 69,83</t>
+          <t>43,74; 62,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,95; 56,44</t>
+          <t>30,49; 52,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 26,28</t>
+          <t>-2,92; 16,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,73; 63,32</t>
+          <t>51,11; 63,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,99; 51,68</t>
+          <t>36,84; 51,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 18,15</t>
+          <t>1,35; 17,49</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>217,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>169,53%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39,92%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>195,5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>153,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>217,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>169,53%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>132,17; 280,75</t>
+          <t>149,26; 311,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,69; 236,69</t>
+          <t>113,4; 259,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 75,76</t>
+          <t>-2,64; 114,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155,71; 316,17</t>
+          <t>129,54; 293,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>109,08; 255,49</t>
+          <t>89,79; 238,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 114,76</t>
+          <t>-9,94; 73,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>158,85; 264,94</t>
+          <t>154,95; 266,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>121,46; 218,41</t>
+          <t>116,15; 215,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 75,46</t>
+          <t>3,97; 70,29</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51,92</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49,01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,82</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>52,43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>40,15</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,57</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51,92</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49,01</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,65</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,6</t>
+          <t>12,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,23; 59,65</t>
+          <t>43,57; 59,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,45; 48,47</t>
+          <t>40,92; 56,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 18,06</t>
+          <t>8,18; 25,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,75; 58,97</t>
+          <t>44,34; 59,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,64; 55,91</t>
+          <t>31,08; 48,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 23,93</t>
+          <t>-2,25; 15,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,36; 57,59</t>
+          <t>46,52; 57,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,06; 51,4</t>
+          <t>38,31; 50,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 18,55</t>
+          <t>5,78; 18,19</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>177,16%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>167,24%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57,39%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>174,02%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>133,28%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>177,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>167,24%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>117,75; 238,6</t>
+          <t>126,35; 248,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,31; 196,65</t>
+          <t>119,0; 239,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 68,59</t>
+          <t>24,25; 103,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125,54; 245,65</t>
+          <t>125,5; 239,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>115,99; 228,5</t>
+          <t>88,55; 196,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 94,92</t>
+          <t>-6,69; 60,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>139,09; 225,05</t>
+          <t>137,6; 221,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>117,4; 195,23</t>
+          <t>114,97; 195,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,77; 70,88</t>
+          <t>17,51; 68,47</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56,1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,62</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-9,93</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>54,61</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>26,24</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-9,81</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56,1</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,62</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,58</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,22</t>
+          <t>-7,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,39; 63,15</t>
+          <t>47,1; 64,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,42; 36,05</t>
+          <t>12,71; 32,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -0,62</t>
+          <t>-18,69; -1,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,24; 64,82</t>
+          <t>45,26; 62,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,81; 31,93</t>
+          <t>15,95; 35,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -1,99</t>
+          <t>-14,98; 2,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,8; 60,98</t>
+          <t>49,35; 61,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 30,99</t>
+          <t>17,61; 31,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,15; -4,08</t>
+          <t>-14,31; -1,84</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>182,71%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-32,35%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>186,42%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>89,58%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-33,5%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>182,71%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-34,45%</t>
+          <t>-19,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,03%</t>
+          <t>-26,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130,06; 278,5</t>
+          <t>126,85; 265,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,97; 149,94</t>
+          <t>35,41; 125,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,98; -3,23</t>
+          <t>-52,38; -5,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125,1; 257,22</t>
+          <t>128,28; 263,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,2; 127,42</t>
+          <t>45,19; 144,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,17; -7,02</t>
+          <t>-44,48; 11,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>140,62; 233,31</t>
+          <t>144,5; 239,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,81; 119,09</t>
+          <t>52,73; 119,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,87; -14,95</t>
+          <t>-42,45; -6,7</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47,31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37,77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>45,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>36,64</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,38</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47,31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>37,77</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-2,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,77; 53,7</t>
+          <t>39,22; 55,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,22; 45,56</t>
+          <t>28,92; 47,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 4,49</t>
+          <t>-9,22; 9,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39,13; 55,23</t>
+          <t>36,45; 53,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,14; 45,89</t>
+          <t>27,96; 45,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 6,9</t>
+          <t>-12,52; 5,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,64; 52,04</t>
+          <t>40,08; 51,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,01; 43,35</t>
+          <t>31,07; 42,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 3,39</t>
+          <t>-8,88; 4,09</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>145,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>115,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-1,57%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>123,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-11,95%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>145,05%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>115,81%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-3,77%</t>
+          <t>-9,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,28%</t>
+          <t>-6,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>85,24; 173,23</t>
+          <t>102,26; 207,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,21; 149,21</t>
+          <t>78,35; 172,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 14,42</t>
+          <t>-25,0; 33,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105,56; 198,08</t>
+          <t>86,73; 172,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>78,52; 164,52</t>
+          <t>65,09; 146,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 23,82</t>
+          <t>-30,69; 16,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>105,8; 170,75</t>
+          <t>102,94; 169,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80,79; 139,03</t>
+          <t>79,92; 137,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 10,17</t>
+          <t>-23,05; 13,24</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53,3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>39,45</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>50,96</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>36,4</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>53,3</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>39,45</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,41; 55,89</t>
+          <t>49,08; 57,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,65; 41,27</t>
+          <t>34,91; 43,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,04</t>
+          <t>0,54; 10,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49,61; 57,63</t>
+          <t>46,51; 55,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,79; 43,89</t>
+          <t>31,47; 40,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 8,85</t>
+          <t>-3,97; 5,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,4; 55,03</t>
+          <t>49,15; 55,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,83; 41,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,66</t>
+          <t>-0,38; 6,52</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>176,04%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>130,28%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>161,23%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>115,17%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-2,41%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>176,04%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>130,28%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>134,55; 195,41</t>
+          <t>147,63; 211,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>89,73; 141,25</t>
+          <t>106,73; 158,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 13,79</t>
+          <t>1,64; 37,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>148,1; 207,39</t>
+          <t>134,61; 191,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>107,23; 158,95</t>
+          <t>91,9; 141,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 31,79</t>
+          <t>-11,49; 17,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>149,52; 190,04</t>
+          <t>150,17; 191,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>106,43; 144,43</t>
+          <t>106,02; 143,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 19,6</t>
+          <t>-1,18; 22,1</t>
         </is>
       </c>
     </row>
